--- a/quizzes/040_foundation_shade_quiz--quizzes.xlsx
+++ b/quizzes/040_foundation_shade_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>foundation_shades</t>
+          <t>foundation_shade_question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Foundation Shades</t>
+          <t>What is your natural skin tone?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>skin_tone</t>
+          <t>foundation_shade_question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Skin Tone</t>
+          <t>What is your undertone?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>undertone</t>
+          <t>foundation_shade_question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Undertone</t>
+          <t>What is your skin type?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>undertone_undertone</t>
+          <t>foundation_shade_question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Undertone</t>
+          <t>Are you looking for a foundation shade that matches your skin tone?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>skin_type</t>
+          <t>foundation_shade_question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Skin Type</t>
+          <t>What is the undertone of your skin?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>skin_type_2</t>
+          <t>foundation_shade_question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Skin Type 2</t>
+          <t>What type of foundation do you want?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>undertone_undertone</t>
+          <t>foundation_shade_question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Undertone</t>
+          <t>Are you looking for a foundation that complements your skin tone?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>skin_tone_2</t>
+          <t>foundation_shade_question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Skin Tone</t>
+          <t>Do you want a foundation that has a matte finish?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>foundation_shade</t>
+          <t>foundation_shade_question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Foundation Shade</t>
+          <t>Do you want a foundation that has a natural finish?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>recommended_shades</t>
+          <t>foundation_shade_question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Recommended Shades</t>
+          <t>Foundation Shade Question 10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>skin_tone_3</t>
+          <t>foundation_shade_question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Skin Tone 3</t>
+          <t>Foundation Shade Question 11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,39 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>undertone_undertone_2</t>
+          <t>foundation_shade_question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Undertone</t>
+          <t>Do you want a foundation with a creamy finish?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>skin_type_3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Skin Type 3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,442 +827,476 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>foundation_shades_choices</t>
+          <t>foundation_shade_question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>foundation_shades_choices</t>
+          <t>foundation_shade_question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>skin_tone_choices</t>
+          <t>foundation_shade_question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dark</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>skin_tone_choices</t>
+          <t>foundation_shade_question_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>cool</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Cool</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>undertone_choices</t>
+          <t>foundation_shade_question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Warm</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>undertone_choices</t>
+          <t>foundation_shade_question_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>undertone_undertone_choices</t>
+          <t>foundation_shade_question_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>undertone_undertone_choices</t>
+          <t>foundation_shade_question_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>skin_type_choices</t>
+          <t>foundation_shade_question_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>skin_type_choices</t>
+          <t>foundation_shade_question_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>skin_type_2_choices</t>
+          <t>foundation_shade_question_5_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cool</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cool</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>skin_type_2_choices</t>
+          <t>foundation_shade_question_5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Warm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>undertone_undertone_choices</t>
+          <t>foundation_shade_question_6_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>matte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Matte</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>undertone_undertone_choices</t>
+          <t>foundation_shade_question_6_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>natural</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Natural</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>skin_tone_2_choices</t>
+          <t>foundation_shade_question_6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>creamy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Creamy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>skin_tone_2_choices</t>
+          <t>foundation_shade_question_7_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foundation_shade_choices</t>
+          <t>foundation_shade_question_7_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foundation_shade_choices</t>
+          <t>foundation_shade_question_8_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>recommended_shades_choices</t>
+          <t>foundation_shade_question_8_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>recommended_shades_choices</t>
+          <t>foundation_shade_question_9_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>skin_tone_3_choices</t>
+          <t>foundation_shade_question_9_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>skin_tone_3_choices</t>
+          <t>foundation_shade_question_10_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>cool</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Cool</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>undertone_undertone_2_choices</t>
+          <t>foundation_shade_question_10_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Warm</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>undertone_undertone_2_choices</t>
+          <t>foundation_shade_question_11_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>skin_type_3_choices</t>
+          <t>foundation_shade_question_11_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>skin_type_3_choices</t>
+          <t>foundation_shade_question_11_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dry</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>foundation_shade_question_12_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>foundation_shade_question_12_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
